--- a/config/union/red_packet.xlsx
+++ b/config/union/red_packet.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="red_packet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="red_packet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1196,7 +1196,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>10</t>
@@ -1247,7 +1246,6 @@
           <t>""</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1352,26 +1350,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1381,7 +1361,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>アリーナで1位獲得</t>
+          <t>在arena获得第一名</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1446,7 +1426,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>アリーナで1位獲得</t>
+          <t>在arena获得第一名</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1469,7 +1449,6 @@
           <t>아레나 결산 1위 필요</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1479,7 +1458,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>戦力が5000に到達</t>
+          <t>战力达到5000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1544,7 +1523,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を5000に到達する</t>
+          <t>战斗力达到5000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1567,7 +1546,6 @@
           <t>전투력 5000 달성 필요</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1577,7 +1555,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>戦力が10000に到達</t>
+          <t>战力达到10000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1642,7 +1620,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を10000に到達する</t>
+          <t>战斗力达到10000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1665,7 +1643,6 @@
           <t>전투력 10000 달성 필요</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1675,7 +1652,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>戦力が30000に到達</t>
+          <t>战斗力达到30000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1740,7 +1717,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を30000に到達する</t>
+          <t>战斗力达到30000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1763,7 +1740,6 @@
           <t>전투력 30000 달성 필요</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1773,7 +1749,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>戦力が50000に到達</t>
+          <t>战力达到50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1838,7 +1814,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を50000に到達する</t>
+          <t>战斗力达到50000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1861,7 +1837,6 @@
           <t>전투력 50000 달성 필요</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1871,7 +1846,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>戦力が75000に到達</t>
+          <t>战力达到75000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1936,7 +1911,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を75000に到達する</t>
+          <t>战斗力达到75000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1959,7 +1934,6 @@
           <t>전투력 75000 달성 필요</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1969,7 +1943,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>戦力が100000に到達</t>
+          <t>战力达到100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2034,7 +2008,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を100000に到達する</t>
+          <t>战斗力达到100000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2057,7 +2031,6 @@
           <t>전투력 100000 달성 필요</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2067,7 +2040,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>戦力が200000に到達</t>
+          <t>战力达到200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2132,7 +2105,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を200000に到達する</t>
+          <t>战斗力达到200000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2155,7 +2128,6 @@
           <t>전투력 200000 달성 필요</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2165,7 +2137,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>戦力が300000に到達</t>
+          <t>战力达到300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2230,7 +2202,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を300000に到達する</t>
+          <t>战斗力达到300000</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2253,7 +2225,6 @@
           <t>전투력 300000 달성 필요</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2263,7 +2234,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>戦力が400000に到達</t>
+          <t>战斗力达到400000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2328,7 +2299,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を400000に到達する</t>
+          <t>战斗力达到400000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2351,7 +2322,6 @@
           <t>전투력 400000 달성 필요</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2361,7 +2331,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>戦力が500000に到達</t>
+          <t>战力达到500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2426,7 +2396,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を500000に到達する</t>
+          <t>战斗力达到500000</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2449,7 +2419,6 @@
           <t>전투력 500000 달성 필요</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2459,7 +2428,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>戦力が600000に到達</t>
+          <t>战力达到600000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2524,7 +2493,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を600000に到達する</t>
+          <t>战斗力达到600000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2547,7 +2516,6 @@
           <t>전투력 600000 달성 필요</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2557,7 +2525,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>戦力が800000に到達</t>
+          <t>战力达到800000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,7 +2590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を800000に到達する</t>
+          <t>战斗力达到800000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2645,7 +2613,6 @@
           <t>전투력 800000 달성 필요</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2655,7 +2622,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>戦力が1000000に到達</t>
+          <t>战力达到1000000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2720,7 +2687,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を1000000に到達する</t>
+          <t>战斗力达到10万</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2743,7 +2710,6 @@
           <t>전투력 1000000 달성 필요</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2753,7 +2719,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>戦力が1200000に到達</t>
+          <t>战力达到1200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2818,7 +2784,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を1200000に到達する</t>
+          <t>战斗力达到1200000</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2841,7 +2807,6 @@
           <t>전투력 1200000 달성 필요</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2851,7 +2816,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>戦力が1400000に到達</t>
+          <t>战力达到1400000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2916,7 +2881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を1400000に到達する</t>
+          <t>战斗力达到1400000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2939,7 +2904,6 @@
           <t>전투력 1400000 달성 필요</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2949,7 +2913,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>戦力が1600000に到達</t>
+          <t>战力达到1600000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3014,7 +2978,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を1600000に到達する</t>
+          <t>战斗力达到1600000</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3037,7 +3001,6 @@
           <t>전투력 1600000 달성 필요</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3047,7 +3010,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>戦力が1800000に到達</t>
+          <t>战力达到1800000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3112,7 +3075,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を1800000に到達する</t>
+          <t>战斗力达到1800000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3135,7 +3098,6 @@
           <t>전투력 1800000 달성 필요</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3145,7 +3107,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>戦力が2000000に到達</t>
+          <t>战力达到2000万</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3210,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を2000000に到達する</t>
+          <t>战斗力达到两千万人</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3233,7 +3195,6 @@
           <t>전투력 2000000 달성 필요</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3243,7 +3204,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>戦力が2200000に到達</t>
+          <t>战力达到2200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3308,7 +3269,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を2200000に到達する</t>
+          <t>战斗力达到2200000</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3331,7 +3292,6 @@
           <t>전투력 2200000 달성 필요</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3341,7 +3301,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>戦力が2400000に到達</t>
+          <t>战力达到2400000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3406,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を2400000に到達する</t>
+          <t>战斗力达到2400000</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3429,7 +3389,6 @@
           <t>전투력 2400000 달성 필요</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3439,7 +3398,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>戦力が2600000に到達</t>
+          <t>战力达到2600000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3504,7 +3463,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を2600000に到達する</t>
+          <t>战斗力达到2600000</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3527,7 +3486,6 @@
           <t>전투력 2600000 달성 필요</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3537,7 +3495,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>戦力が2800000に到達</t>
+          <t>战力达到2800000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3602,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を2800000に到達する</t>
+          <t>战斗力达到2800000</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3625,7 +3583,6 @@
           <t>전투력 2800000 달성 필요</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3635,7 +3592,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>戦力が3000000に到達</t>
+          <t>战力达到3000000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3700,7 +3657,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を3000000に到達する</t>
+          <t>战斗力达到3000万</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3723,7 +3680,6 @@
           <t>전투력 3000000 달성 필요</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3733,7 +3689,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>戦力が3500000に到達</t>
+          <t>战力达到3500000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3798,7 +3754,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を3500000に到達する</t>
+          <t>战斗力达到3500000</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3821,7 +3777,6 @@
           <t>전투력 3500000 달성 필요</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3831,7 +3786,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>戦力が4000000に到達</t>
+          <t>战斗力达到4000000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3896,7 +3851,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を4000000に到達する</t>
+          <t>战斗力达到4000000</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3919,7 +3874,6 @@
           <t>전투력 4000000 달성 필요</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3929,7 +3883,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>戦力が4500000に到達</t>
+          <t>战力达到4500000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3994,7 +3948,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を4500000に到達する</t>
+          <t>战斗力达到4500000</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4017,7 +3971,6 @@
           <t>전투력 4500000 달성 필요</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4027,7 +3980,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>戦力が5000000に到達</t>
+          <t>战力达到5000万</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4092,7 +4045,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を5000000に到達する</t>
+          <t>战斗力达到5000万</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4115,7 +4068,6 @@
           <t>전투력 5000000 달성 필요</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4125,7 +4077,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>戦力が5500000に到達</t>
+          <t>战力达到5500000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4190,7 +4142,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を5500000に到達する</t>
+          <t>战斗力达到5500000</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4213,7 +4165,6 @@
           <t>전투력 5500000 달성 필요</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4223,7 +4174,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>戦力が6000000に到達</t>
+          <t>战力达到6000000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4288,7 +4239,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を6000000に到達する</t>
+          <t>战斗力达到6000000</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4311,7 +4262,6 @@
           <t>전투력 6000000 달성 필요</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4321,7 +4271,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>戦力が6500000に到達</t>
+          <t>战力达到6500000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4386,7 +4336,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を6500000に到達する</t>
+          <t>战斗力达到6500000</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4409,7 +4359,6 @@
           <t>전투력 6500000 달성 필요</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4419,7 +4368,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>戦力が7000000に到達</t>
+          <t>战力达到7000万</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4484,7 +4433,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を7000000に到達する</t>
+          <t>战斗力达到7000万</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4507,7 +4456,6 @@
           <t>전투력 7000000 달성 필요</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4517,7 +4465,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>戦力が7500000に到達</t>
+          <t>战力达到7500000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4582,7 +4530,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を7500000に到達する</t>
+          <t>战斗力达到7500000</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4605,7 +4553,6 @@
           <t>전투력 7500000 달성 필요</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4615,7 +4562,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>戦力が8000000に到達</t>
+          <t>战力达到8000万</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4680,7 +4627,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を8000000に到達する</t>
+          <t>战斗力达到8000万</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4703,7 +4650,6 @@
           <t>전투력 8000000 달성 필요</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4713,7 +4659,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>戦力が8500000に到達</t>
+          <t>战力达到8500000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4778,7 +4724,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を8500000に到達する</t>
+          <t>战斗力达到8500000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4801,7 +4747,6 @@
           <t>전투력 8500000 달성 필요</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4811,7 +4756,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>戦力が9000000に到達</t>
+          <t>战力达到9000万</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4876,7 +4821,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を9000000に到達する</t>
+          <t>战斗力达到9000万</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4899,7 +4844,6 @@
           <t>전투력 9000000 달성 필요</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4909,7 +4853,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>戦力が9500000に到達</t>
+          <t>战斗力达到9500000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4974,7 +4918,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を9500000に到達する</t>
+          <t>战斗力达到9500000</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4997,7 +4941,6 @@
           <t>전투력 9500000 달성 필요</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5007,7 +4950,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>戦力が10000000に到達</t>
+          <t>战力达到10000000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5072,7 +5015,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>戦闘力を10000000に到達する</t>
+          <t>战斗力达到10000000</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5095,29 +5038,10 @@
           <t>전투력 10000000 달성 필요</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5127,7 +5051,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.10に到達</t>
+          <t>角色达到Lv.10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5192,7 +5116,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>チームLv.10に到達する</t>
+          <t>队伍达到Lv.10</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5215,7 +5139,6 @@
           <t>팀 레벨 10 달성 필요</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5225,7 +5148,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.20に到達</t>
+          <t>角色达到Lv.20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5290,7 +5213,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>チームLv.20に到達する</t>
+          <t>队伍达到Lv.20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5313,7 +5236,6 @@
           <t>팀 레벨 20 달성 필요</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5323,7 +5245,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.30に到達</t>
+          <t>角色达到Lv.30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5388,7 +5310,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>チームLv.30に到達する</t>
+          <t>队伍达到Lv.30</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5411,7 +5333,6 @@
           <t>팀 레벨 30 달성 필요</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5421,7 +5342,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.40に到達</t>
+          <t>角色达到Lv.40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5486,7 +5407,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>チームLv.40に到達する</t>
+          <t>队伍达到Lv.40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5509,7 +5430,6 @@
           <t>팀 레벨 40 달성 필요</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5519,7 +5439,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.60に到達</t>
+          <t>角色达到Lv.60</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5584,7 +5504,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>チームLv.60に到達する</t>
+          <t>队伍达到Lv.60</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5607,7 +5527,6 @@
           <t>팀 레벨 60 달성 필요</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5617,7 +5536,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.80に到達</t>
+          <t>角色达到Lv.80</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5682,7 +5601,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>チームLv.80に到達する</t>
+          <t>队伍达到Lv.80</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5705,7 +5624,6 @@
           <t>팀 레벨 80 달성 필요</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5715,7 +5633,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.90に到達</t>
+          <t>角色达到Lv.90</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5780,7 +5698,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>チームLv.90に到達する</t>
+          <t>队伍达到Lv.90</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5803,7 +5721,6 @@
           <t>팀 레벨 90 달성 필요</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5813,7 +5730,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.99に到達</t>
+          <t>角色达到Lv.99</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5878,7 +5795,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>チームLv.99に到達する</t>
+          <t>达到Lv.99队</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5901,7 +5818,6 @@
           <t>팀 레벨 99 달성 필요</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5911,7 +5827,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>キャラがLv.104に到達</t>
+          <t>角色达到Lv.104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5976,7 +5892,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>チームLv.104に到達する</t>
+          <t>到达Lv.104队</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5999,29 +5915,10 @@
           <t>팀 레벨 104 달성 필요</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6031,7 +5928,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ステージ1-6をクリア</t>
+          <t>完成关卡1-6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6095,10 +5992,6 @@
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
           <t>10105</t>
@@ -6113,7 +6006,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ステージ3-8をクリア</t>
+          <t>完成关卡3-8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6177,10 +6070,6 @@
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
           <t>10308</t>
@@ -6195,7 +6084,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ステージ5-10をクリア</t>
+          <t>完成5-10关卡</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6259,10 +6148,6 @@
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
           <t>10510</t>
@@ -6277,7 +6162,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ステージ7-10をクリア</t>
+          <t>完成7-10关卡</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6341,10 +6226,6 @@
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
           <t>10710</t>
@@ -6359,7 +6240,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ステージ9-10をクリア</t>
+          <t>完成9-10关卡</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6423,10 +6304,6 @@
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
           <t>10910</t>
@@ -6441,7 +6318,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ステージ11-10をクリア</t>
+          <t>完成11-10关卡</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6505,10 +6382,6 @@
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
           <t>11110</t>
@@ -6523,7 +6396,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ステージ13-10をクリア</t>
+          <t>完成13-10关卡</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6587,10 +6460,6 @@
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
           <t>11310</t>
@@ -6605,7 +6474,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ステージ15-10をクリア</t>
+          <t>完成15-10关卡</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6669,10 +6538,6 @@
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
           <t>11510</t>
@@ -6687,7 +6552,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ステージ17-10をクリア</t>
+          <t>完成关卡17-10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6751,10 +6616,6 @@
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
           <t>11710</t>
@@ -6769,7 +6630,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ステージ19-10をクリア</t>
+          <t>完成19-10关卡</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6833,10 +6694,6 @@
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
           <t>11910</t>
@@ -6851,7 +6708,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ステージ21-10をクリア</t>
+          <t>完成21-10关卡</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6915,10 +6772,6 @@
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
           <t>12110</t>
@@ -6933,7 +6786,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ステージ22-10をクリア</t>
+          <t>完成22-10关卡</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6997,10 +6850,6 @@
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
           <t>12210</t>
@@ -7008,26 +6857,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7037,7 +6868,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>本日チャージ3280</t>
+          <t>今日充值3280</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7101,10 +6932,6 @@
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7119,7 +6946,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>本日チャージ6480</t>
+          <t>今日充值6480</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7183,10 +7010,6 @@
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7201,7 +7024,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.5に到達</t>
+          <t>VIP达到Lv.5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7265,10 +7088,6 @@
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7283,7 +7102,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.7に到達</t>
+          <t>VIP达到Lv.7</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7347,10 +7166,6 @@
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7365,7 +7180,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.10に到達</t>
+          <t>VIP达到Lv.10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7429,10 +7244,6 @@
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7447,7 +7258,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.12に到達</t>
+          <t>VIP达到Lv.12</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7511,10 +7322,6 @@
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7529,7 +7336,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.15に到達</t>
+          <t>VIP达到Lv.15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7593,10 +7400,6 @@
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7611,7 +7414,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.16に到達</t>
+          <t>VIP等级达到Lv.16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7675,10 +7478,6 @@
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7693,7 +7492,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.17に到達</t>
+          <t>VIP等级达到Lv.17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7757,10 +7556,6 @@
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7775,7 +7570,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VIPがLv.18に到達</t>
+          <t>VIP达到Lv.18</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7839,10 +7634,6 @@
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
           <t>recharge</t>
@@ -7850,26 +7641,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7879,7 +7652,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ハードモード3-1クリア</t>
+          <t>硬模式3-1清除</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7943,10 +7716,6 @@
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
           <t>30301</t>
@@ -7961,7 +7730,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ハードモード6-1クリア</t>
+          <t>硬模式6-1清除</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8025,10 +7794,6 @@
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr">
         <is>
           <t>30601</t>
@@ -8043,7 +7808,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ハードモード9-1クリア</t>
+          <t>硬模式9-1清除</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8107,10 +7872,6 @@
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
           <t>30901</t>
@@ -8125,7 +7886,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ハードモード12-1クリア</t>
+          <t>硬模式12-1清除</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8189,10 +7950,6 @@
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
           <t>31201</t>
@@ -8207,7 +7964,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ハードモード15-1クリア</t>
+          <t>硬模式15-1清除</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8271,10 +8028,6 @@
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
           <t>31501</t>
@@ -8289,7 +8042,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ハードモード18-1クリア</t>
+          <t>硬模式18-1清除</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8353,10 +8106,6 @@
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr">
         <is>
           <t>31801</t>
@@ -8371,7 +8120,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ハードモード21-1クリア</t>
+          <t>硬模式21-1清除</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8435,10 +8184,6 @@
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
           <t>32101</t>
@@ -8453,7 +8198,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ハードモード22-1クリア</t>
+          <t>硬模式22-1清除</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8517,10 +8262,6 @@
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr">
         <is>
           <t>32201</t>
